--- a/diagram_link.xlsx
+++ b/diagram_link.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phase-Figs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A6E54E-90E9-4F58-AECB-F420644C9A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEE8EF2-67CD-448B-AD1B-4B976BE977DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1788" windowWidth="14856" windowHeight="9456" xr2:uid="{80B65B43-CEF6-4492-9EFE-1C88CB529E1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{80B65B43-CEF6-4492-9EFE-1C88CB529E1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>Ag-Si</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -200,9 +200,6 @@
   </si>
   <si>
     <t>https://www.crct.polymtl.ca/fact/phase_diagram.php?file=NaF-SrF2.jpg&amp;dir=Ftsalt</t>
-  </si>
-  <si>
-    <t>PuF3-ThF4</t>
   </si>
   <si>
     <t>https://www.crct.polymtl.ca/fact/phase_diagram.php?file=PuF3-ThF4.jpg&amp;dir=Ftsalt</t>
@@ -229,6 +226,18 @@
   </si>
   <si>
     <t>Ref_URL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sn-Bi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PuF3-ThF4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.crct.polymtl.ca/fact/phase_diagram.php?file=Bi-Sn.jpg&amp;dir=Fslead</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -277,7 +286,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -300,6 +309,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -309,12 +329,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -322,6 +341,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -638,255 +659,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9937EF-51AA-401B-9498-5F8167A54E4E}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="74.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="74.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="6" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -920,6 +945,7 @@
     <hyperlink ref="B28" r:id="rId27" tooltip="autolink" display="https://link.wtturl.cn/?target=https%3A%2F%2Fwww.crct.polymtl.ca%2Ffact%2Fphase_diagram.php%3Ffile%3DNaF-RbF.jpg%26dir%3DFtsalt&amp;scene=im&amp;aid=582478&amp;lang=zh" xr:uid="{7A262D6A-5C7B-42B4-AC8E-F58F72026AE2}"/>
     <hyperlink ref="B29" r:id="rId28" tooltip="autolink" display="https://link.wtturl.cn/?target=https%3A%2F%2Fwww.crct.polymtl.ca%2Ffact%2Fphase_diagram.php%3Ffile%3DNaF-SrF2.jpg%26dir%3DFtsalt&amp;scene=im&amp;aid=582478&amp;lang=zh" xr:uid="{90BBB131-53AD-470C-9B6B-CE68DBE7869E}"/>
     <hyperlink ref="B30" r:id="rId29" tooltip="autolink" display="https://link.wtturl.cn/?target=https%3A%2F%2Fwww.crct.polymtl.ca%2Ffact%2Fphase_diagram.php%3Ffile%3DPuF3-ThF4.jpg%26dir%3DFtsalt&amp;scene=im&amp;aid=582478&amp;lang=zh" xr:uid="{3EB3A005-1D4D-4AFC-999C-59EA8D00BFC6}"/>
+    <hyperlink ref="B31" r:id="rId30" xr:uid="{3F38CA69-94BA-4F9E-BFE5-2FB881D2B998}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/diagram_link.xlsx
+++ b/diagram_link.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phase-Figs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEE8EF2-67CD-448B-AD1B-4B976BE977DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B18F57-FEBF-4B93-9ADC-EB60FBCA28B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{80B65B43-CEF6-4492-9EFE-1C88CB529E1E}"/>
   </bookViews>
@@ -229,15 +229,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Sn-Bi</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PuF3-ThF4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>https://www.crct.polymtl.ca/fact/phase_diagram.php?file=Bi-Sn.jpg&amp;dir=Fslead</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bi-Sn</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -286,7 +286,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -309,17 +309,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -329,7 +318,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -341,8 +330,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -899,18 +886,18 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
